--- a/KAMCHATKA_ZAPOLNENIE/02_ООО_ДН_РУ.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/02_ООО_ДН_РУ.xlsx
@@ -2456,11 +2456,31 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n"/>
-      <c r="V19" s="8" t="n"/>
-      <c r="W19" s="8" t="n"/>
-      <c r="X19" s="8" t="n"/>
-      <c r="Y19" s="8" t="n"/>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду25 Ру16 фланцевый, Kvy - 3.2м3/ч, Tmax 150°С, уплотнение - EPD</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» (ИНН 0323085570)</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
       <c r="Z19" s="8" t="n"/>
       <c r="AA19" s="9" t="n"/>
       <c r="AB19" s="10">
@@ -2687,11 +2707,31 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n"/>
-      <c r="V21" s="8" t="n"/>
-      <c r="W21" s="8" t="n"/>
-      <c r="X21" s="8" t="n"/>
-      <c r="Y21" s="8" t="n"/>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду50 Ру16 фланцевый, Kvy - 32м3/ч, Tmax 150°С, уплотнение - EPDM</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» (ИНН 0323085570)</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
       <c r="Z21" s="8" t="n"/>
       <c r="AA21" s="9" t="n"/>
       <c r="AB21" s="10">
@@ -2808,11 +2848,31 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n"/>
-      <c r="V22" s="8" t="n"/>
-      <c r="W22" s="8" t="n"/>
-      <c r="X22" s="8" t="n"/>
-      <c r="Y22" s="8" t="n"/>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Регулятор давления после себя Энерготехномаш УРРД-НО-РД Ду80 Ру25 фланцевый, Kvy - 25м3/ч, Tmax 220°С, уплотнение - PTFE</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» (ИНН 0323085570)</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
       <c r="Z22" s="8" t="n"/>
       <c r="AA22" s="9" t="n"/>
       <c r="AB22" s="10">
@@ -3574,11 +3634,31 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n"/>
-      <c r="V29" s="8" t="n"/>
-      <c r="W29" s="8" t="n"/>
-      <c r="X29" s="8" t="n"/>
-      <c r="Y29" s="8" t="n"/>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>Клапан обратный Dendor 010C Ду200 Ру16 межфланцевый, двухстворчатый, корпус - чугун, диск - чугун, уплотнение - 1 шт EPD</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>АО «Энергия» (ИНН 7805499441)</t>
+        </is>
+      </c>
+      <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
+        <is>
+          <t>10743786</t>
+        </is>
+      </c>
+      <c r="Y29" s="7" t="inlineStr">
+        <is>
+          <t>08.12.2030</t>
+        </is>
+      </c>
       <c r="Z29" s="8" t="n"/>
       <c r="AA29" s="9" t="n"/>
       <c r="AB29" s="10">
@@ -3765,7 +3845,7 @@
       </c>
       <c r="V31" s="7" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (ИНН 7718625072)</t>
         </is>
       </c>
       <c r="W31" s="7" t="inlineStr">
@@ -3773,8 +3853,16 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X31" s="8" t="n"/>
-      <c r="Y31" s="8" t="n"/>
+      <c r="X31" s="7" t="inlineStr">
+        <is>
+          <t>10618660</t>
+        </is>
+      </c>
+      <c r="Y31" s="7" t="inlineStr">
+        <is>
+          <t>17.03.2028</t>
+        </is>
+      </c>
       <c r="Z31" s="8" t="n"/>
       <c r="AA31" s="9" t="n"/>
       <c r="AB31" s="10">
